--- a/KPI.xlsx
+++ b/KPI.xlsx
@@ -8,12 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dmart_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5C9E1EF-698E-4233-B9F2-498B5A8FD40F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1AF63D-DAAD-452A-A348-53788D520BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{343193CF-69E0-46CE-A856-02DB6398B96E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{343193CF-69E0-46CE-A856-02DB6398B96E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="48">
   <si>
     <t>ORD100000</t>
   </si>
@@ -69,13 +73,127 @@
   </si>
   <si>
     <t>find avg value net rev</t>
+  </si>
+  <si>
+    <t>empid</t>
+  </si>
+  <si>
+    <t>Empid</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Nagpur</t>
+  </si>
+  <si>
+    <t>Pune</t>
+  </si>
+  <si>
+    <t>Nashik</t>
+  </si>
+  <si>
+    <t>Goa</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Roll No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phy </t>
+  </si>
+  <si>
+    <t>Chem</t>
+  </si>
+  <si>
+    <t>Maths</t>
+  </si>
+  <si>
+    <t>jan</t>
+  </si>
+  <si>
+    <t>feb</t>
+  </si>
+  <si>
+    <t>mar</t>
+  </si>
+  <si>
+    <t>apr</t>
+  </si>
+  <si>
+    <t>may</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>january</t>
+  </si>
+  <si>
+    <t>february</t>
+  </si>
+  <si>
+    <t>march</t>
+  </si>
+  <si>
+    <t>april</t>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>meena</t>
+  </si>
+  <si>
+    <t>Ansh</t>
+  </si>
+  <si>
+    <t>Vishal</t>
+  </si>
+  <si>
+    <t>Shiva</t>
+  </si>
+  <si>
+    <t>Diya</t>
+  </si>
+  <si>
+    <t>Daksh</t>
+  </si>
+  <si>
+    <t>diya</t>
+  </si>
+  <si>
+    <t>daksh</t>
+  </si>
+  <si>
+    <t>ansh</t>
+  </si>
+  <si>
+    <t>vishal</t>
+  </si>
+  <si>
+    <t>shiva</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -88,16 +206,35 @@
       <color theme="1"/>
       <name val="Cambria"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF00B050"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -105,20 +242,215 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="darkDown">
+          <fgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="darkDown">
+          <fgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="darkDown">
+          <fgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -503,7 +835,7 @@
         <v>0.38</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D5" si="0">B3*C3</f>
+        <f t="shared" ref="D3:D4" si="0">B3*C3</f>
         <v>1445.1286</v>
       </c>
       <c r="E3">
@@ -571,4 +903,443 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26DCB66D-97EB-4A77-93D5-EBBBD418B70A}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="11.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>101</v>
+      </c>
+      <c r="B2">
+        <v>110</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2">
+        <v>41895</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>102</v>
+      </c>
+      <c r="B3">
+        <v>120</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="E3" s="2">
+        <v>41896</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>103</v>
+      </c>
+      <c r="B4">
+        <v>130</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2">
+        <v>41897</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>104</v>
+      </c>
+      <c r="B5">
+        <v>140</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2">
+        <v>41898</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>105</v>
+      </c>
+      <c r="B6">
+        <v>150</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="E6" s="2">
+        <v>41899</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>106</v>
+      </c>
+      <c r="B7">
+        <v>160</v>
+      </c>
+      <c r="C7">
+        <v>15</v>
+      </c>
+      <c r="E7" s="2">
+        <v>41900</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>107</v>
+      </c>
+      <c r="B8">
+        <v>170</v>
+      </c>
+      <c r="C8">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2">
+        <v>41901</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>108</v>
+      </c>
+      <c r="B9">
+        <v>180</v>
+      </c>
+      <c r="C9">
+        <v>19</v>
+      </c>
+      <c r="E9" s="2">
+        <v>41902</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64CC1318-97EF-45AE-8BFB-7D8FB5C5FF7A}">
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>101</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>102</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>103</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>104</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>105</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Column Error" error="Invalid City please select city from enlisted citys_x000a_" sqref="B2:B13" xr:uid="{D93EC3E5-3E76-40C3-BFD9-F3B322B29323}">
+      <formula1>"Nagpur, Pune, Nashik, Goa"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Column Error" error="Age must be 21 or greater then 21_x000a_" sqref="C2:C12" xr:uid="{0F6FEAB3-83E0-47E9-AAB3-56D356950D24}">
+      <formula1>21</formula1>
+      <formula2>45</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C05675AE-AC43-4785-87C8-5B851B2DA6FC}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A57D8C81-83EB-49C6-BC69-91D664A7DB48}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>101</v>
+      </c>
+      <c r="B2">
+        <v>56</v>
+      </c>
+      <c r="C2">
+        <v>78</v>
+      </c>
+      <c r="D2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>102</v>
+      </c>
+      <c r="B3">
+        <v>45</v>
+      </c>
+      <c r="C3">
+        <v>76</v>
+      </c>
+      <c r="D3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>103</v>
+      </c>
+      <c r="B4">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>54</v>
+      </c>
+      <c r="D4">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>104</v>
+      </c>
+      <c r="B5">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>35</v>
+      </c>
+      <c r="D5">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B2:B5">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C5">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFC000"/>
+        <color theme="7" tint="0.39997558519241921"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:D5 B6:B8" xr:uid="{09F3520E-0024-46FE-9E55-2720BB8FF784}">
+      <formula1>40</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>